--- a/artfynd/A 1585-2025 artfynd.xlsx
+++ b/artfynd/A 1585-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125041968</v>
+        <v>125041862</v>
       </c>
       <c r="B2" t="n">
         <v>56722</v>
@@ -730,14 +730,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trehörningen, Trehörningen, Vstm</t>
+          <t>Långbrokärret, Långbrokärret, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477349</v>
+        <v>477331</v>
       </c>
       <c r="R2" t="n">
-        <v>6598630</v>
+        <v>6598505</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +769,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125041862</v>
+        <v>125041788</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477331</v>
+        <v>477341</v>
       </c>
       <c r="R3" t="n">
-        <v>6598505</v>
+        <v>6598466</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125041788</v>
+        <v>125041968</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -992,14 +992,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långbrokärret, Långbrokärret, Vstm</t>
+          <t>Trehörningen, Trehörningen, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477341</v>
+        <v>477349</v>
       </c>
       <c r="R4" t="n">
-        <v>6598466</v>
+        <v>6598630</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 1585-2025 artfynd.xlsx
+++ b/artfynd/A 1585-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125041862</v>
+        <v>125041878</v>
       </c>
       <c r="B2" t="n">
         <v>56722</v>
@@ -725,7 +725,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477331</v>
+        <v>477336</v>
       </c>
       <c r="R2" t="n">
-        <v>6598505</v>
+        <v>6598498</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +769,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125041788</v>
+        <v>125041862</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477341</v>
+        <v>477331</v>
       </c>
       <c r="R3" t="n">
-        <v>6598466</v>
+        <v>6598505</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1068,7 +1068,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125041878</v>
+        <v>125041788</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477336</v>
+        <v>477341</v>
       </c>
       <c r="R5" t="n">
-        <v>6598498</v>
+        <v>6598466</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1585-2025 artfynd.xlsx
+++ b/artfynd/A 1585-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125041862</v>
+        <v>125041788</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477331</v>
+        <v>477341</v>
       </c>
       <c r="R3" t="n">
-        <v>6598505</v>
+        <v>6598466</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1068,7 +1068,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125041788</v>
+        <v>125041862</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477341</v>
+        <v>477331</v>
       </c>
       <c r="R5" t="n">
-        <v>6598466</v>
+        <v>6598505</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1585-2025 artfynd.xlsx
+++ b/artfynd/A 1585-2025 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125041878</v>
+        <v>125041968</v>
       </c>
       <c r="B2" t="n">
         <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -725,19 +725,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långbrokärret, Långbrokärret, Vstm</t>
+          <t>Trehörningen, Trehörningen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477336</v>
+        <v>477349</v>
       </c>
       <c r="R2" t="n">
-        <v>6598498</v>
+        <v>6598630</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +769,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -813,7 +813,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -937,14 +937,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125041968</v>
+        <v>125041862</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -992,14 +992,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Trehörningen, Trehörningen, Vstm</t>
+          <t>Långbrokärret, Långbrokärret, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477349</v>
+        <v>477331</v>
       </c>
       <c r="R4" t="n">
-        <v>6598630</v>
+        <v>6598505</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,14 +1068,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125041862</v>
+        <v>125041878</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477331</v>
+        <v>477336</v>
       </c>
       <c r="R5" t="n">
-        <v>6598505</v>
+        <v>6598498</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1585-2025 artfynd.xlsx
+++ b/artfynd/A 1585-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125041968</v>
+        <v>125041862</v>
       </c>
       <c r="B2" t="n">
         <v>56722</v>
@@ -730,14 +730,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trehörningen, Trehörningen, Vstm</t>
+          <t>Långbrokärret, Långbrokärret, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477349</v>
+        <v>477331</v>
       </c>
       <c r="R2" t="n">
-        <v>6598630</v>
+        <v>6598505</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +769,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,14 +806,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125041788</v>
+        <v>125041878</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477341</v>
+        <v>477336</v>
       </c>
       <c r="R3" t="n">
-        <v>6598466</v>
+        <v>6598498</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125041862</v>
+        <v>125041788</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477331</v>
+        <v>477341</v>
       </c>
       <c r="R4" t="n">
-        <v>6598505</v>
+        <v>6598466</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,14 +1068,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125041878</v>
+        <v>125041968</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1118,19 +1118,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långbrokärret, Långbrokärret, Vstm</t>
+          <t>Trehörningen, Trehörningen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477336</v>
+        <v>477349</v>
       </c>
       <c r="R5" t="n">
-        <v>6598498</v>
+        <v>6598630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1585-2025 artfynd.xlsx
+++ b/artfynd/A 1585-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125041862</v>
+        <v>125041968</v>
       </c>
       <c r="B2" t="n">
         <v>56722</v>
@@ -730,14 +730,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långbrokärret, Långbrokärret, Vstm</t>
+          <t>Trehörningen, Trehörningen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477331</v>
+        <v>477349</v>
       </c>
       <c r="R2" t="n">
-        <v>6598505</v>
+        <v>6598630</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +769,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,14 +806,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125041878</v>
+        <v>125041788</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477336</v>
+        <v>477341</v>
       </c>
       <c r="R3" t="n">
-        <v>6598498</v>
+        <v>6598466</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,14 +937,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125041788</v>
+        <v>125041878</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477341</v>
+        <v>477336</v>
       </c>
       <c r="R4" t="n">
-        <v>6598466</v>
+        <v>6598498</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,7 +1068,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125041968</v>
+        <v>125041862</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1123,14 +1123,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Trehörningen, Trehörningen, Vstm</t>
+          <t>Långbrokärret, Långbrokärret, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477349</v>
+        <v>477331</v>
       </c>
       <c r="R5" t="n">
-        <v>6598630</v>
+        <v>6598505</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1585-2025 artfynd.xlsx
+++ b/artfynd/A 1585-2025 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125041968</v>
+        <v>125041878</v>
       </c>
       <c r="B2" t="n">
         <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -725,19 +725,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trehörningen, Trehörningen, Vstm</t>
+          <t>Långbrokärret, Långbrokärret, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477349</v>
+        <v>477336</v>
       </c>
       <c r="R2" t="n">
-        <v>6598630</v>
+        <v>6598498</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +769,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125041788</v>
+        <v>125041862</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477341</v>
+        <v>477331</v>
       </c>
       <c r="R3" t="n">
-        <v>6598466</v>
+        <v>6598505</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,14 +937,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125041878</v>
+        <v>125041788</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477336</v>
+        <v>477341</v>
       </c>
       <c r="R4" t="n">
-        <v>6598498</v>
+        <v>6598466</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,7 +1068,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125041862</v>
+        <v>125041968</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1123,14 +1123,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långbrokärret, Långbrokärret, Vstm</t>
+          <t>Trehörningen, Trehörningen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477331</v>
+        <v>477349</v>
       </c>
       <c r="R5" t="n">
-        <v>6598505</v>
+        <v>6598630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1585-2025 artfynd.xlsx
+++ b/artfynd/A 1585-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125041862</v>
+        <v>125041788</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477331</v>
+        <v>477341</v>
       </c>
       <c r="R3" t="n">
-        <v>6598505</v>
+        <v>6598466</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125041788</v>
+        <v>125041862</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477341</v>
+        <v>477331</v>
       </c>
       <c r="R4" t="n">
-        <v>6598466</v>
+        <v>6598505</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 1585-2025 artfynd.xlsx
+++ b/artfynd/A 1585-2025 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125041878</v>
+        <v>125041862</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477336</v>
+        <v>477331</v>
       </c>
       <c r="R2" t="n">
-        <v>6598498</v>
+        <v>6598505</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +769,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,14 +806,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125041788</v>
+        <v>125041878</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477341</v>
+        <v>477336</v>
       </c>
       <c r="R3" t="n">
-        <v>6598466</v>
+        <v>6598498</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125041862</v>
+        <v>125041968</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -992,14 +992,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långbrokärret, Långbrokärret, Vstm</t>
+          <t>Trehörningen, Trehörningen, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477331</v>
+        <v>477349</v>
       </c>
       <c r="R4" t="n">
-        <v>6598505</v>
+        <v>6598630</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,10 +1068,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125041968</v>
+        <v>125041788</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,14 +1123,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Trehörningen, Trehörningen, Vstm</t>
+          <t>Långbrokärret, Långbrokärret, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477349</v>
+        <v>477341</v>
       </c>
       <c r="R5" t="n">
-        <v>6598630</v>
+        <v>6598466</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1585-2025 artfynd.xlsx
+++ b/artfynd/A 1585-2025 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125041862</v>
+        <v>125041878</v>
       </c>
       <c r="B2" t="n">
         <v>56836</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477331</v>
+        <v>477336</v>
       </c>
       <c r="R2" t="n">
-        <v>6598505</v>
+        <v>6598498</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +769,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,14 +806,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125041878</v>
+        <v>125041788</v>
       </c>
       <c r="B3" t="n">
         <v>56836</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477336</v>
+        <v>477341</v>
       </c>
       <c r="R3" t="n">
-        <v>6598498</v>
+        <v>6598466</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125041968</v>
+        <v>125041862</v>
       </c>
       <c r="B4" t="n">
         <v>56836</v>
@@ -992,14 +992,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Trehörningen, Trehörningen, Vstm</t>
+          <t>Långbrokärret, Långbrokärret, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477349</v>
+        <v>477331</v>
       </c>
       <c r="R4" t="n">
-        <v>6598630</v>
+        <v>6598505</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,7 +1068,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125041788</v>
+        <v>125041968</v>
       </c>
       <c r="B5" t="n">
         <v>56836</v>
@@ -1123,14 +1123,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långbrokärret, Långbrokärret, Vstm</t>
+          <t>Trehörningen, Trehörningen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477341</v>
+        <v>477349</v>
       </c>
       <c r="R5" t="n">
-        <v>6598466</v>
+        <v>6598630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1585-2025 artfynd.xlsx
+++ b/artfynd/A 1585-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125041878</v>
+        <v>125041968</v>
       </c>
       <c r="B2" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -725,19 +720,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långbrokärret, Långbrokärret, Vstm</t>
+          <t>Trehörningen, Trehörningen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477336</v>
+        <v>477349</v>
       </c>
       <c r="R2" t="n">
-        <v>6598498</v>
+        <v>6598630</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,12 +804,7 @@
         <v>125041788</v>
       </c>
       <c r="B3" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,12 +930,7 @@
         <v>125041862</v>
       </c>
       <c r="B4" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,15 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125041968</v>
+        <v>125041878</v>
       </c>
       <c r="B5" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,19 +1098,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Trehörningen, Trehörningen, Vstm</t>
+          <t>Långbrokärret, Långbrokärret, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477349</v>
+        <v>477336</v>
       </c>
       <c r="R5" t="n">
-        <v>6598630</v>
+        <v>6598498</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1162,7 +1142,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1172,7 +1152,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
